--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N82_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N82_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.25321359620719</v>
+        <v>6.378647209383669</v>
       </c>
       <c r="D2" t="n">
-        <v>39.37903529941349</v>
+        <v>6.399093236154693</v>
       </c>
       <c r="E2" t="n">
-        <v>14.41178008904146</v>
+        <v>2.341914264469238</v>
       </c>
       <c r="F2" t="n">
-        <v>13.620584709442</v>
+        <v>2.213345015284326</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.37612929074729</v>
+        <v>4.936121009746436</v>
       </c>
       <c r="D3" t="n">
-        <v>30.53411630668555</v>
+        <v>4.961793899836402</v>
       </c>
       <c r="E3" t="n">
-        <v>14.41178008904146</v>
+        <v>2.341914264469238</v>
       </c>
       <c r="F3" t="n">
-        <v>13.620584709442</v>
+        <v>2.213345015284326</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>57.49248911710333</v>
+        <v>9.34252948152929</v>
       </c>
       <c r="D4" t="n">
-        <v>49.25547268403621</v>
+        <v>8.004014311155885</v>
       </c>
       <c r="E4" t="n">
-        <v>14.41178008904146</v>
+        <v>2.341914264469238</v>
       </c>
       <c r="F4" t="n">
-        <v>13.620584709442</v>
+        <v>2.213345015284326</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.62808135457494</v>
+        <v>4.977063220118429</v>
       </c>
       <c r="D5" t="n">
-        <v>30.67382979465018</v>
+        <v>4.984497341630654</v>
       </c>
       <c r="E5" t="n">
-        <v>14.41178008904146</v>
+        <v>2.341914264469238</v>
       </c>
       <c r="F5" t="n">
-        <v>13.620584709442</v>
+        <v>2.213345015284326</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>18.00805127384416</v>
+        <v>2.926308331999677</v>
       </c>
       <c r="D6" t="n">
-        <v>18.0972729944906</v>
+        <v>2.940806861604723</v>
       </c>
       <c r="E6" t="n">
-        <v>14.41178008904146</v>
+        <v>2.341914264469238</v>
       </c>
       <c r="F6" t="n">
-        <v>13.620584709442</v>
+        <v>2.213345015284326</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.35801185159572</v>
+        <v>4.933176925884305</v>
       </c>
       <c r="D7" t="n">
-        <v>30.197849084632</v>
+        <v>4.907150476252701</v>
       </c>
       <c r="E7" t="n">
-        <v>14.41178008904146</v>
+        <v>2.341914264469238</v>
       </c>
       <c r="F7" t="n">
-        <v>13.620584709442</v>
+        <v>2.213345015284326</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.81455696165497</v>
+        <v>5.819865506268932</v>
       </c>
       <c r="D8" t="n">
-        <v>35.66524585544612</v>
+        <v>5.795602451509994</v>
       </c>
       <c r="E8" t="n">
-        <v>14.41178008904146</v>
+        <v>2.341914264469238</v>
       </c>
       <c r="F8" t="n">
-        <v>13.620584709442</v>
+        <v>2.213345015284326</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>54.32669283370038</v>
+        <v>8.828087585476313</v>
       </c>
       <c r="D9" t="n">
-        <v>54.72297907194145</v>
+        <v>8.892484099190485</v>
       </c>
       <c r="E9" t="n">
-        <v>14.41178008904146</v>
+        <v>2.341914264469238</v>
       </c>
       <c r="F9" t="n">
-        <v>13.620584709442</v>
+        <v>2.213345015284326</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>64.1439456788336</v>
+        <v>10.42339117281046</v>
       </c>
       <c r="D10" t="n">
-        <v>64.51660723982526</v>
+        <v>10.48394867647161</v>
       </c>
       <c r="E10" t="n">
-        <v>14.41178008904146</v>
+        <v>2.341914264469238</v>
       </c>
       <c r="F10" t="n">
-        <v>13.620584709442</v>
+        <v>2.213345015284326</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
